--- a/Decks/Elfos.xlsx
+++ b/Decks/Elfos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A8D7BD-3356-4031-8EBC-7AD5888BAFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D3BB1A-2AD5-4E15-9A5F-0FB360CB82FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{721EE551-19A8-4AC6-A026-FA1528AD395E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{721EE551-19A8-4AC6-A026-FA1528AD395E}"/>
   </bookViews>
   <sheets>
     <sheet name="Elfos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
   <si>
     <t>Função</t>
   </si>
@@ -387,9 +387,6 @@
   </si>
   <si>
     <t>Tireless Provisioner</t>
-  </si>
-  <si>
-    <t>Emeritus of Abundance</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1752,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -1770,7 +1767,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -1785,7 +1782,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -1800,7 +1797,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -1815,7 +1812,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -1830,7 +1827,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -1845,7 +1842,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -1860,7 +1857,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -1875,7 +1872,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -1890,7 +1887,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -1905,7 +1902,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -1920,7 +1917,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -1935,7 +1932,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -1950,7 +1947,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -1965,7 +1962,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -1979,11 +1976,8 @@
       <c r="D79" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E79" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>78</v>
       </c>

--- a/Decks/Elfos.xlsx
+++ b/Decks/Elfos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D3BB1A-2AD5-4E15-9A5F-0FB360CB82FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDC71E4-12BD-4B43-A277-1560E7C5FF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{721EE551-19A8-4AC6-A026-FA1528AD395E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{721EE551-19A8-4AC6-A026-FA1528AD395E}"/>
   </bookViews>
   <sheets>
     <sheet name="Elfos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="116">
   <si>
     <t>Função</t>
   </si>
@@ -339,9 +339,6 @@
   </si>
   <si>
     <t>Proteção</t>
-  </si>
-  <si>
-    <t>Reclamation Sage</t>
   </si>
   <si>
     <t>Elvish Soultiller</t>
@@ -969,7 +966,7 @@
         <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1176,10 +1173,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1614,7 +1611,7 @@
         <v>55</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1941,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1956,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>83</v>
@@ -2019,7 +2016,7 @@
         <v>65</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2208,13 +2205,13 @@
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2226,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -2241,70 +2238,70 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>103</v>
+      </c>
+      <c r="B98" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="D98" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Elfos.xlsx
+++ b/Decks/Elfos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDC71E4-12BD-4B43-A277-1560E7C5FF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30975990-923A-4049-9354-900761368F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{721EE551-19A8-4AC6-A026-FA1528AD395E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="119">
   <si>
     <t>Função</t>
   </si>
@@ -384,6 +384,15 @@
   </si>
   <si>
     <t>Tireless Provisioner</t>
+  </si>
+  <si>
+    <t>Forbidden Orchard</t>
+  </si>
+  <si>
+    <t>Mutavault</t>
+  </si>
+  <si>
+    <t>Shang-Chi, Master of Kung Fu</t>
   </si>
 </sst>
 </file>
@@ -885,10 +894,10 @@
       </c>
       <c r="B7" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>14</v>
@@ -903,10 +912,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1083,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>29</v>
@@ -1188,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1848,25 +1857,25 @@
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -1878,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -1893,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -1908,10 +1917,10 @@
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1919,14 +1928,14 @@
         <v>78</v>
       </c>
       <c r="B76" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C76&lt;&gt;D76</f>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -1934,14 +1943,14 @@
         <v>78</v>
       </c>
       <c r="B77" s="5" t="b">
-        <f>C77&lt;&gt;D77</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1950,13 +1959,13 @@
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -1968,25 +1977,25 @@
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1994,14 +2003,14 @@
         <v>86</v>
       </c>
       <c r="B81" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C81&lt;&gt;D81</f>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2009,14 +2018,14 @@
         <v>86</v>
       </c>
       <c r="B82" s="5" t="b">
-        <f>C82&lt;&gt;D82</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2028,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2043,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -2058,10 +2067,10 @@
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -2073,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -2088,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -2103,10 +2112,10 @@
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -2118,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2133,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2148,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2163,10 +2172,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2178,25 +2187,25 @@
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2208,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2223,25 +2232,25 @@
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="B97" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C97&lt;&gt;D97</f>
+        <v>1</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">

--- a/Decks/Elfos.xlsx
+++ b/Decks/Elfos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30975990-923A-4049-9354-900761368F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAEFE25-AAF4-47BC-928B-EEB8D6515F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{721EE551-19A8-4AC6-A026-FA1528AD395E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="120">
   <si>
     <t>Função</t>
   </si>
@@ -215,9 +215,6 @@
     <t>Fyndhorn Elves</t>
   </si>
   <si>
-    <t>Jaspera Sentinel</t>
-  </si>
-  <si>
     <t>Gwenna, Eyes of Gaea</t>
   </si>
   <si>
@@ -380,9 +377,6 @@
     <t>Eclipsed Realms</t>
   </si>
   <si>
-    <t>Prosperous Innkeeper</t>
-  </si>
-  <si>
     <t>Tireless Provisioner</t>
   </si>
   <si>
@@ -393,6 +387,15 @@
   </si>
   <si>
     <t>Shang-Chi, Master of Kung Fu</t>
+  </si>
+  <si>
+    <t>Elven Raft-Steerer</t>
+  </si>
+  <si>
+    <t>Woodland Weavemaster</t>
+  </si>
+  <si>
+    <t>Elven Passage</t>
   </si>
 </sst>
 </file>
@@ -912,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -975,7 +978,7 @@
         <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1182,10 +1185,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1197,10 +1200,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1209,13 +1212,13 @@
       </c>
       <c r="B28" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1482,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1620,7 +1623,7 @@
         <v>55</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1677,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1692,625 +1695,625 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="D61" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="D64" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" ref="B65:B101" si="1">C65&lt;&gt;D65</f>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="D69" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="D72" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B76" s="5" t="b">
         <f>C76&lt;&gt;D76</f>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="D80" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B81" s="5" t="b">
         <f>C81&lt;&gt;D81</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B95" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="D95" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B97" s="5" t="b">
         <f>C97&lt;&gt;D97</f>
         <v>1</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="D98" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
